--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,363 +656,375 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2902000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2006000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1435000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>3750000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>245000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2157000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1270000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>882000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2585000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>380000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3">
         <v>2928000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6731000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2209000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1738000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1548000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>259500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5382200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>659600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>184100</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="3">
         <v>4935200</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>842000</v>
+      </c>
+      <c r="E9" s="3">
         <v>872000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>808000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>831000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>837000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>819000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>847000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>761000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>741000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>783000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>902000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>805000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>837000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>820000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>165000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>160000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>135000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>137000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-232000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>-188000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>-464700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>612600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>-504400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>-584300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>-876200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>838900</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-674000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2030000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1198000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>604000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-1270000</v>
-      </c>
       <c r="H10" s="3">
+        <v>-1308000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2931000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-602000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1396000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>529000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1105000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-20000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1780000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-457000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1584000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3">
         <v>2768000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6596000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2072000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1970000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1736000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>724200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4769600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1164000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>768400</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3">
         <v>4096300</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,8 +1054,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1125,8 +1138,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1208,8 +1224,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1252,8 +1271,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1291,8 +1310,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1374,8 +1396,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1402,174 +1427,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1529000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1607000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1533000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1545000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1518000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1496000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1567000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1503000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1419000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1468000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1589000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1431000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1457000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1436000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-511000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>408000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2531000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-412000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>959000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1317000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>763700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1915500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>756600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>635200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1255700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2961300</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1361000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1295000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>473000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-110000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1951000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1989000</v>
+      </c>
+      <c r="I18" s="3">
         <v>2254000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1322000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>654000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-149000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1790000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-707000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1154000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1077000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2200000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>2520000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4200000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2621000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>779000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>231000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-504200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3466700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-97000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-451100</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>1973900</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1599,151 +1631,155 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2053000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1670000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>788000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-226000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2203000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2246000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1747000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1172000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-516000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2718000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1223000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2376000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2570000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>34000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-37000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>27000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-27600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>124800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-58800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-108000</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>692000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-375000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-315000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>116000</v>
       </c>
-      <c r="G21" s="3">
-        <v>252000</v>
-      </c>
       <c r="H21" s="3">
+        <v>214000</v>
+      </c>
+      <c r="I21" s="3">
         <v>8000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>425000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-518000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>367000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>928000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1930000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3530000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1493000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2026000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>2554000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4163000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2633000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>766000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,43 +1801,46 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E22" s="3">
         <v>25000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>43000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>44000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>63000</v>
       </c>
       <c r="H22" s="3">
         <v>25000</v>
       </c>
       <c r="I22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J22" s="3">
         <v>45000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>61000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>49000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>25000</v>
       </c>
       <c r="M22" s="3">
         <v>25000</v>
       </c>
       <c r="N22" s="3">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="O22" s="3">
         <v>28000</v>
@@ -1810,212 +1849,221 @@
         <v>28000</v>
       </c>
       <c r="Q22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="R22" s="3">
         <v>40000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>29000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>31400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>41800</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>665000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-400000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-358000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>72000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>189000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>380000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-579000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>318000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>903000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3502000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1465000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2525000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4139000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2613000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>748000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>252000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-538400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3585400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-163200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-531900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1824100</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>20000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-172000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-19000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-113000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>36000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>101000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-395000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>712000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>245000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-558000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-385000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>657000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>845000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>388000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>87000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-16000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-54500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>585600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-273100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-157000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-457000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>33200</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2097,174 +2145,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>660000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-420000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-186000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>91000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>185000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>358000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-466000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>282000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>802000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2790000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1220000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1868000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3294000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2225000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>661000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>268000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-483900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2999800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>109900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-374900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1790900</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-435000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-215000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>65000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>168000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>334000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-480000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>264000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>784000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2762000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1204000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1879000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3263000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2194000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>585000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>206000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-540000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2931500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>75700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-396600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1796700</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2346,8 +2403,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2429,8 +2489,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2512,8 +2575,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2595,174 +2661,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2053000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1670000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-788000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>226000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2203000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2246000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1747000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1172000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>516000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2718000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1223000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2376000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2570000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>174000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>-34000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>37000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-27000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>27600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-124800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>58800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>73000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>108000</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>655000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-424000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-204000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>179000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>345000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-469000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>275000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>795000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1559000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2773000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1217000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1879000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3263000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2194000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>585000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>206000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-540000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2931500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>75700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-396600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1796700</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2844,179 +2919,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>655000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-424000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-204000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>179000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>345000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-469000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>275000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>795000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1559000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2773000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1217000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1879000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3263000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2194000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>585000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>206000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-540000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2931500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>75700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-396600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1796700</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3046,8 +3130,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3077,77 +3162,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5986000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5539000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5704000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4562000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3784000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3887000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3767000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3061000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1736000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2542000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2688000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2760000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2100000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1779000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4298000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5331000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5258000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2674000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2623000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2481800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1534600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1572600</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3160,8 +3246,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3172,41 +3261,41 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>230000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>109000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>107000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>77000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>76000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>75000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>73000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>71000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>106000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>108000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3243,8 +3332,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3287,8 +3379,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3326,8 +3418,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3370,8 +3465,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3409,53 +3504,56 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27622000</v>
+      </c>
+      <c r="E45" s="3">
         <v>27085000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28585000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29531000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30077000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29504000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31673000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31542000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33116000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33405000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33205000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34619000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34689000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35061000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3492,53 +3590,56 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33608000</v>
+      </c>
+      <c r="E46" s="3">
         <v>32624000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34289000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34323000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33970000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33498000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35443000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34680000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>34931000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36024000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35969000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37455000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36898000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36950000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3575,77 +3676,80 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>59083000</v>
+      </c>
+      <c r="E47" s="3">
         <v>55087000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>53799000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>52453000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>49851000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>48375000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>46037000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47832000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45464000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44795000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45101000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44820000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>47663000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>49584000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>69762000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>63940000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>65884000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>68419000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>72810000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>73061400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>73253400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>74850100</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,52 +3762,55 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>54000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>20000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>24000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -3741,53 +3848,56 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11655000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11634000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11660000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11654000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11681000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11770000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11887000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11986000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12066000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12173000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12302000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12447000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12599000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12760000</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -3824,8 +3934,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3907,8 +4020,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3990,77 +4106,80 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>246617000</v>
+      </c>
+      <c r="E52" s="3">
         <v>224707000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>237428000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>240148000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>233381000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>218735000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>230269000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>236188000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>229979000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>231799000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>221257000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>204200000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>213946000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>205647000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>320000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>759000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>981000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1343000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>954000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1004600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>892500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1076100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4073,8 +4192,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4156,77 +4278,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>367065000</v>
+      </c>
+      <c r="E54" s="3">
         <v>339537000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>352586000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>353558000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>343722000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>327193000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>338450000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>345662000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>337776000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>340280000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>330255000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>314534000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>326980000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>321464000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>314983000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>302970000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>316205000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>352641000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>375559000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>364372500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>366657400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>355242300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4239,8 +4364,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4270,8 +4398,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4301,53 +4430,54 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14090000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14511000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14960000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15498000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15740000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16275000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16742000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18103000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18465000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19244000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19952000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19973000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>21170000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22254000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -4384,53 +4514,56 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E58" s="3">
         <v>505000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1047000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1032000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1253000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1134000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2431000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>907000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2476000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2008000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>401000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>979000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2518000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1870000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4440,15 +4573,15 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>1601700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4467,77 +4600,80 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4039000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4552000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4069000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4024000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3958000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4622000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4108000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4846000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4727000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5035000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6643000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6564000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6536000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7467000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>291108000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>284311000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>297972000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>334931000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>357851000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>345753500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>348610300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>337134500</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4550,53 +4686,56 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18606000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19568000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20689000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20554000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20951000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22031000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23899000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23856000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25668000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26287000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27555000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27516000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30224000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31591000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4633,76 +4772,79 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5243000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4570000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4653000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4648000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4669000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4333000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4403000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4399000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4075000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4101000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4057000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4046000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4030000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4050000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>2634000</v>
       </c>
       <c r="S61" s="3">
         <v>2634000</v>
       </c>
       <c r="T61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="U61" s="3">
         <v>2640000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2649000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="W61" s="3">
-        <v>317700</v>
       </c>
       <c r="X61" s="3">
         <v>317700</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
@@ -4716,53 +4858,56 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>332742000</v>
+      </c>
+      <c r="E62" s="3">
         <v>305499000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>316902000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>317855000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>307500000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>290304000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>300166000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>306500000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>297749000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>299536000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>288309000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>272719000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>283303000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>276356000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -4799,8 +4944,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4882,8 +5030,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4965,8 +5116,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5048,77 +5202,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>356591000</v>
+      </c>
+      <c r="E66" s="3">
         <v>329637000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>342244000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>343057000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>333120000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>316668000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>328468000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>334755000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>327492000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>329924000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>319921000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>304281000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>317557000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>311997000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>306337000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>293996000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>306642000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>343067000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>365165000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>354114300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>356266900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>345258400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5131,8 +5288,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5162,8 +5322,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5245,8 +5406,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5328,8 +5492,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5373,7 +5540,7 @@
         <v>533000</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -5411,8 +5578,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5494,77 +5664,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7549000</v>
+      </c>
+      <c r="E72" s="3">
         <v>6968000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7471000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7741000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7733000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7623000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7713000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7431000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7965000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7766000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7038000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8661000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5952000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4852000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6403000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9065000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7635000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4782000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2809000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2284600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2076800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2617900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5577,8 +5750,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5660,8 +5836,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5743,8 +5922,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5826,77 +6008,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9429000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8963000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9420000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9696000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9821000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9768000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9231000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10165000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9551000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9636000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9637000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8945000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8119000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8105000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8646000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8974000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9563000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9574000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10394000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10258200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10390500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9983900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6094,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5992,179 +6180,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>655000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-424000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-204000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>179000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>345000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-469000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>275000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>795000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1559000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2773000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1217000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1879000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3263000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2194000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>585000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>206000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-540000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2931500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>75700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-396600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1796700</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6194,8 +6391,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6238,8 +6436,8 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -6277,8 +6475,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6360,8 +6561,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6443,8 +6647,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6526,8 +6733,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6609,8 +6819,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6692,91 +6905,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1849000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1045000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1621000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1370000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1173000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1594000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1525000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1364000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1478000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1426000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1634000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1129000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1086000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1461000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2265000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>845000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1236000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>860000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2166400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1429200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>803400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1344000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1329700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1045800</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6806,8 +7025,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6850,8 +7070,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -6889,8 +7109,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6972,8 +7195,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7055,91 +7281,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3017000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2430000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2094000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2765000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-953000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2769000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-401000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>93000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2119000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>78000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-146000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2817000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-202000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>44100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>2079600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-629800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7169,68 +7401,69 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E96" s="3">
         <v>64000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>54000</v>
       </c>
       <c r="F96" s="3">
         <v>54000</v>
       </c>
       <c r="G96" s="3">
+        <v>54000</v>
+      </c>
+      <c r="H96" s="3">
         <v>57000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>58000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>51000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>53000</v>
       </c>
       <c r="K96" s="3">
         <v>53000</v>
       </c>
       <c r="L96" s="3">
+        <v>53000</v>
+      </c>
+      <c r="M96" s="3">
         <v>54000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>141000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>51000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>50000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>51000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-35000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-49000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-50000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-52000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-50000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7252,8 +7485,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7335,8 +7571,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7418,8 +7657,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7501,91 +7743,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1615000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1220000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1465000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1502000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1489000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-521000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1950000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>359000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-369000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>433000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-842000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>538000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-624000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-582000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-78000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-484500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-290500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-129100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>530500</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7628,8 +7876,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7667,87 +7915,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-165000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1142000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>778000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-103000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>120000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>706000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1322000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-805000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-147000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-74000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>662000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>322000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>75000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2586000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>49000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>148900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>947200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-38000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-446100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>570800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
